--- a/content/tasks.xlsx
+++ b/content/tasks.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -28,6 +28,9 @@
     <t>领取条件</t>
   </si>
   <si>
+    <t>完成条件</t>
+  </si>
+  <si>
     <t>资金</t>
   </si>
   <si>
@@ -64,13 +67,16 @@
     <t/>
   </si>
   <si>
+    <t>{"statsSumAtLeast":120}</t>
+  </si>
+  <si>
     <t>{"flagsContain":["ev:debut"]}</t>
   </si>
   <si>
-    <t>四项属性总和达到出道门槛后，点「出道」。完成后回来领奖。</t>
-  </si>
-  <si>
-    <t>达到出道条件并完成出道</t>
+    <t>四项属性总和达到出道门槛后，领取任务，然后点「出道」。</t>
+  </si>
+  <si>
+    <t>完成出道</t>
   </si>
   <si>
     <t>task-dance-30</t>
@@ -79,13 +85,16 @@
     <t>舞蹈三十</t>
   </si>
   <si>
+    <t>{"statsAtLeast":{"dance":20}}</t>
+  </si>
+  <si>
     <t>{"statsAtLeast":{"dance":30}}</t>
   </si>
   <si>
     <t>把舞蹈练到 30，说明你已经不是新人了。</t>
   </si>
   <si>
-    <t>舞蹈属性达到 30</t>
+    <t>舞蹈练到 30</t>
   </si>
   <si>
     <t>task-first-show</t>
@@ -103,7 +112,7 @@
     <t>{"fansAtLeast":{"stage":100}}</t>
   </si>
   <si>
-    <t>演出会把路人变成粉丝。攒到 100 舞台粉就能领一次。</t>
+    <t>演出会把路人变成粉丝。攒到 100 舞台粉。</t>
   </si>
   <si>
     <t>舞台粉累计到 100</t>
@@ -113,6 +122,9 @@
   </si>
   <si>
     <t>攒到一万</t>
+  </si>
+  <si>
+    <t>{"moneyAtLeast":5000}</t>
   </si>
   <si>
     <t>{"moneyAtLeast":10000}</t>
@@ -522,20 +534,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="4" max="6" width="18" customWidth="1"/>
+    <col min="7" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,209 +587,227 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2">
+        <v>3000</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>3000</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2">
-        <v>100</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2">
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3">
+        <v>500</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4">
+        <v>800</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>500</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3">
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>20</v>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4">
-        <v>800</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>200</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6">
-        <v>200</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
       <c r="L6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6">
         <v>50</v>
       </c>
     </row>
